--- a/data/RGPV_Result_0105IT2410_1-2.xlsx
+++ b/data/RGPV_Result_0105IT2410_1-2.xlsx
@@ -460,7 +460,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
   </cols>
@@ -723,7 +723,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Fail in IT305- [T]</t>
+          <t>Fail in IT305</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
